--- a/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0001T0006Z000C1N4_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0001T0006Z000C1N4_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>15.51229198923015</v>
+        <v>2.520747448249899</v>
       </c>
       <c r="D2" t="n">
-        <v>17.93437366586433</v>
+        <v>2.914335720702953</v>
       </c>
       <c r="E2" t="n">
-        <v>9.203680884969446</v>
+        <v>1.495598143807535</v>
       </c>
       <c r="F2" t="n">
-        <v>3.373941246866845</v>
+        <v>0.5482654526158626</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>33.91965375916904</v>
+        <v>5.51194373586497</v>
       </c>
       <c r="D3" t="n">
-        <v>24.68225615959802</v>
+        <v>4.010866625934678</v>
       </c>
       <c r="E3" t="n">
-        <v>9.203680884969446</v>
+        <v>1.495598143807535</v>
       </c>
       <c r="F3" t="n">
-        <v>3.373941246866845</v>
+        <v>0.5482654526158626</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
